--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486853_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486853_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0368</v>
+        <v>6.4429</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4297</v>
+        <v>6.1619</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6071</v>
+        <v>0.281</v>
       </c>
       <c r="G2" t="n">
         <v>4.2067</v>
@@ -610,13 +610,13 @@
         <v>1.0267</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.3246</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.651</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5694</v>
+        <v>0.2434</v>
       </c>
       <c r="V2" t="n">
         <v>2.117</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6949</v>
+        <v>2.2487</v>
       </c>
       <c r="E3" t="n">
-        <v>3.418</v>
+        <v>2.713</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2768</v>
+        <v>-0.4642</v>
       </c>
       <c r="G3" t="n">
         <v>-0.7946</v>
@@ -688,13 +688,13 @@
         <v>1.0267</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5902</v>
+        <v>1.144</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4992</v>
+        <v>0.7941</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0909</v>
+        <v>0.3499</v>
       </c>
       <c r="V3" t="n">
         <v>1.8993</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2684</v>
+        <v>1.6258</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3059</v>
+        <v>1.5151</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0375</v>
+        <v>0.1107</v>
       </c>
       <c r="G4" t="n">
         <v>1.1606</v>
@@ -766,13 +766,13 @@
         <v>0.8214</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0092</v>
+        <v>-0.6518</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4611</v>
+        <v>-0.2519</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5481</v>
+        <v>-0.3999</v>
       </c>
       <c r="V4" t="n">
         <v>1.5277</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. CLEMENT AIGBOGUN</t>
+          <t>V. PEREZ TOMAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7986</v>
+        <v>1.4212</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5285</v>
+        <v>2.2185</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2701</v>
+        <v>-0.7973</v>
       </c>
       <c r="G5" t="n">
-        <v>0.992</v>
+        <v>1.7602</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5709</v>
+        <v>-0.2759</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4211</v>
+        <v>2.0361</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5623</v>
+        <v>3.191</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.3893</v>
       </c>
       <c r="L5" t="n">
-        <v>0.605</v>
+        <v>2.8017</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5702</v>
+        <v>-1.4308</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3863</v>
+        <v>-0.6653</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1839</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="P5" t="n">
+        <v>-0.616</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-1.2321</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-2.2588</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3405</v>
+        <v>0.277</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0464</v>
+        <v>0.2595</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2941</v>
+        <v>0.0175</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. PEREZ TOMAS</t>
+          <t>K. CLEMENT AIGBOGUN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6544</v>
+        <v>1.2746</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6296</v>
+        <v>0.7377</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9752</v>
+        <v>0.5369</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7602</v>
+        <v>0.992</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2759</v>
+        <v>0.5709</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0361</v>
+        <v>0.4211</v>
       </c>
       <c r="J6" t="n">
-        <v>3.191</v>
+        <v>1.5623</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3893</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>2.8017</v>
+        <v>0.605</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4308</v>
+        <v>-0.5702</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6653</v>
+        <v>-0.3863</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.1839</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.616</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.2321</v>
+        <v>-2.2588</v>
       </c>
       <c r="R6" t="n">
-        <v>0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4897</v>
+        <v>0.8165</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3294</v>
+        <v>0.2556</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1604</v>
+        <v>0.5609</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.327</v>
+        <v>0.994</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4603</v>
+        <v>3.8012</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.1333</v>
+        <v>-2.8072</v>
       </c>
       <c r="G7" t="n">
         <v>0.439</v>
@@ -1000,13 +1000,13 @@
         <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9334</v>
+        <v>-0.2663</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0386</v>
+        <v>0.3796</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.972</v>
+        <v>-0.6459</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1512</v>
+        <v>-0.502</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0161</v>
+        <v>-1.1594</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8649</v>
+        <v>0.6574</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4855</v>
@@ -1078,13 +1078,13 @@
         <v>0.616</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0201</v>
+        <v>0.6693</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1045</v>
+        <v>-0.0388</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9156</v>
+        <v>0.7081</v>
       </c>
       <c r="V8" t="n">
         <v>0.6982</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PALAMOS MOLINS</t>
+          <t>E. HERRERA SAURET</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.9268999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3683</v>
+        <v>-0.0905</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.138</v>
+        <v>-0.8363</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7474</v>
+        <v>-1.4441</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7527</v>
+        <v>1.6871</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9947</v>
+        <v>-3.1312</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2329</v>
+        <v>0.3707</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0229</v>
+        <v>1.7393</v>
       </c>
       <c r="L9" t="n">
-        <v>1.21</v>
+        <v>-1.3686</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.9804</v>
+        <v>-1.8147</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7756</v>
+        <v>-0.0522</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.2047</v>
+        <v>-1.7626</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2053</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4233</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3675</v>
+        <v>0.5306</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0559</v>
+        <v>0.3973</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X9" t="n">
         <v>-0.2402</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>J. PALAMOS MOLINS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4884</v>
+        <v>-1.2516</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3139</v>
+        <v>0.7679</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1745</v>
+        <v>-2.0194</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.4035</v>
+        <v>-1.7474</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.1697</v>
+        <v>-0.7527</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2338</v>
+        <v>-0.9947</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5152</v>
+        <v>1.2329</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.673</v>
+        <v>0.0229</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1579</v>
+        <v>1.21</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8883</v>
+        <v>-2.9804</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4967</v>
+        <v>-0.7756</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3917</v>
+        <v>-2.2047</v>
       </c>
       <c r="P10" t="n">
-        <v>0.616</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.4107</v>
+        <v>-1.2321</v>
       </c>
       <c r="R10" t="n">
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2991</v>
+        <v>0.9414</v>
       </c>
       <c r="T10" t="n">
-        <v>0.612</v>
+        <v>0.767</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6871</v>
+        <v>0.1744</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. HERRERA SAURET</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7076</v>
+        <v>-1.9051</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5748</v>
+        <v>-1.5231</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1328</v>
+        <v>-0.382</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4441</v>
+        <v>-3.4035</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6871</v>
+        <v>-2.1697</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.1312</v>
+        <v>-1.2338</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3707</v>
+        <v>-1.5152</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7393</v>
+        <v>-1.673</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3686</v>
+        <v>0.1579</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8147</v>
+        <v>-1.8883</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0522</v>
+        <v>-0.4967</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7626</v>
+        <v>-1.3917</v>
       </c>
       <c r="P11" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-0.4107</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-1.2321</v>
-      </c>
       <c r="R11" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1472</v>
+        <v>0.8824</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0464</v>
+        <v>0.4028</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1008</v>
+        <v>0.4796</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.2349</v>
+        <v>-5.3346</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1978</v>
+        <v>-3.4458</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.037</v>
+        <v>-1.8888</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3539</v>
@@ -1390,13 +1390,13 @@
         <v>1.4374</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7884</v>
+        <v>0.6887</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3093</v>
+        <v>1.0614</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5209</v>
+        <v>-0.3727</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5893</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4283</v>
+        <v>4.086999999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>11.0377</v>
+        <v>11.6965</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.6094</v>
+        <v>-7.6092</v>
       </c>
       <c r="G13" t="n">
         <v>-3.6705</v>
       </c>
       <c r="H13" t="n">
-        <v>3.065399999999999</v>
+        <v>3.0654</v>
       </c>
       <c r="I13" t="n">
         <v>-6.736000000000001</v>
@@ -1468,19 +1468,19 @@
         <v>10.2671</v>
       </c>
       <c r="S13" t="n">
-        <v>5.0949</v>
+        <v>5.753699999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5824</v>
+        <v>4.241099999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5124</v>
+        <v>1.5126</v>
       </c>
       <c r="V13" t="n">
         <v>6.110900000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>6.853999999999999</v>
+        <v>6.854</v>
       </c>
       <c r="X13" t="n">
         <v>-0.7430999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1944</v>
+        <v>3.1683</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8077</v>
+        <v>4.4939</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6133</v>
+        <v>-1.3256</v>
       </c>
       <c r="G14" t="n">
         <v>2.9716</v>
@@ -1546,13 +1546,13 @@
         <v>1.8481</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8389</v>
+        <v>-0.865</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2245</v>
+        <v>-0.0893</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0633</v>
+        <v>-0.7756</v>
       </c>
       <c r="V14" t="n">
         <v>0.2402</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3599</v>
+        <v>2.6353</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7953</v>
+        <v>1.1091</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5646</v>
+        <v>1.5263</v>
       </c>
       <c r="G15" t="n">
         <v>2.9205</v>
@@ -1624,13 +1624,13 @@
         <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3471</v>
+        <v>-0.0717</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3798</v>
+        <v>-0.066</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0327</v>
+        <v>-0.0057</v>
       </c>
       <c r="V15" t="n">
         <v>-0.8295</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. ZHAO OLMOS</t>
+          <t>D. ARJOL LOPEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9785</v>
+        <v>1.8017</v>
       </c>
       <c r="E16" t="n">
-        <v>4.7796</v>
+        <v>2.0311</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.801</v>
+        <v>-0.2294</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7333</v>
+        <v>2.6559</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0839</v>
+        <v>2.2612</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3506</v>
+        <v>0.3947</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3842</v>
+        <v>3.8522</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1354</v>
+        <v>2.0897</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2488</v>
+        <v>1.7626</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.6509</v>
+        <v>-1.1963</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0516</v>
+        <v>0.1716</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.5993</v>
+        <v>-1.3679</v>
       </c>
       <c r="P16" t="n">
-        <v>1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2321</v>
+        <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0132</v>
+        <v>0.5298</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2167</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2036</v>
+        <v>0.5377</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1786</v>
+        <v>0.2402</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1786</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. ARJOL LOPEZ</t>
+          <t>J. ZHAO OLMOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7791</v>
+        <v>1.5217</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8219</v>
+        <v>4.3612</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0428</v>
+        <v>-2.8394</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6559</v>
+        <v>0.7333</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2612</v>
+        <v>1.0839</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3947</v>
+        <v>-0.3506</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8522</v>
+        <v>3.3842</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0897</v>
+        <v>2.1354</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7626</v>
+        <v>1.2488</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1963</v>
+        <v>-2.6509</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1716</v>
+        <v>-1.0516</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3679</v>
+        <v>-1.5993</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8481</v>
+        <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5072</v>
+        <v>-0.4436</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2171</v>
+        <v>-0.2017</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7243000000000001</v>
+        <v>-0.2419</v>
       </c>
       <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.1786</v>
+      </c>
+      <c r="X17" t="n">
         <v>-1.1786</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.2402</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-1.4189</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0713</v>
+        <v>0.2632</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1803</v>
+        <v>1.0757</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.109</v>
+        <v>-0.8126</v>
       </c>
       <c r="G18" t="n">
         <v>3.1407</v>
@@ -1858,13 +1858,13 @@
         <v>2.0534</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8641</v>
+        <v>-0.6722</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0854</v>
+        <v>-0.19</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.4823</v>
       </c>
       <c r="V18" t="n">
         <v>-1.1786</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3636</v>
+        <v>0.1873</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6571</v>
+        <v>-0.3433</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2935</v>
+        <v>0.5306</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2659</v>
@@ -1936,13 +1936,13 @@
         <v>1.2321</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3297</v>
+        <v>-0.7788</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.651</v>
+        <v>-0.3372</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6787</v>
+        <v>-0.4416</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1827</v>
+        <v>-0.7503</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3422</v>
+        <v>0.656</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5249</v>
+        <v>-1.4064</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3745</v>
@@ -2014,13 +2014,13 @@
         <v>1.0267</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.8349</v>
+        <v>-1.4025</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8486</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9863</v>
+        <v>-0.8677</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0262</v>
+        <v>-2.9147</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3014</v>
+        <v>-1.0922</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7248</v>
+        <v>-1.8225</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6845</v>
@@ -2092,13 +2092,13 @@
         <v>1.8481</v>
       </c>
       <c r="S21" t="n">
-        <v>0.303</v>
+        <v>0.4145</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1513</v>
+        <v>0.0579</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4543</v>
+        <v>0.3566</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4661</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6262</v>
+        <v>-3.9854</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4836</v>
+        <v>-2.902</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1426</v>
+        <v>-1.0834</v>
       </c>
       <c r="G22" t="n">
         <v>-5.1263</v>
@@ -2170,13 +2170,13 @@
         <v>1.0267</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4734</v>
+        <v>0.1143</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6701</v>
+        <v>0.2517</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1967</v>
+        <v>-0.1374</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6128</v>
+        <v>-4.6581</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6755</v>
+        <v>-1.7801</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9373</v>
+        <v>-2.878</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3001</v>
@@ -2248,13 +2248,13 @@
         <v>0.616</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1771</v>
+        <v>-1.2224</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2907</v>
+        <v>-0.3953</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8863</v>
+        <v>-0.8270999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6982</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4283</v>
+        <v>-2.731000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>7.609400000000001</v>
+        <v>7.609400000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>-11.0376</v>
+        <v>-10.3404</v>
       </c>
       <c r="G24" t="n">
         <v>3.6707</v>
@@ -2326,13 +2326,13 @@
         <v>14.374</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.095</v>
+        <v>-4.3976</v>
       </c>
       <c r="T24" t="n">
         <v>-1.5126</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.5823</v>
+        <v>-2.885</v>
       </c>
       <c r="V24" t="n">
         <v>-6.1108</v>
